--- a/AtchisonRegime/Outputs/UK/df_regZScores_UK.xlsx
+++ b/AtchisonRegime/Outputs/UK/df_regZScores_UK.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E341"/>
+  <dimension ref="A1:E342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6062,7 +6062,7 @@
         <v>-1.19358360560507</v>
       </c>
       <c r="C331" t="n">
-        <v>0.09340882308341358</v>
+        <v>0.07964939555553918</v>
       </c>
       <c r="D331" t="n">
         <v>0.6607631425232638</v>
@@ -6079,7 +6079,7 @@
         <v>-1.346897329223275</v>
       </c>
       <c r="C332" t="n">
-        <v>0.0900835623051776</v>
+        <v>0.09572965693366631</v>
       </c>
       <c r="D332" t="n">
         <v>0.6738196246178002</v>
@@ -6096,7 +6096,7 @@
         <v>-1.368891981285238</v>
       </c>
       <c r="C333" t="n">
-        <v>0.06848008446736131</v>
+        <v>0.07146216020915283</v>
       </c>
       <c r="D333" t="n">
         <v>0.64392862120351</v>
@@ -6113,7 +6113,7 @@
         <v>-1.329356106593292</v>
       </c>
       <c r="C334" t="n">
-        <v>0.01849161531362393</v>
+        <v>0.02267314646484296</v>
       </c>
       <c r="D334" t="n">
         <v>0.5453937035152667</v>
@@ -6130,7 +6130,7 @@
         <v>-1.347299861214833</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.02802955874058935</v>
+        <v>-0.02431350306585164</v>
       </c>
       <c r="D335" t="n">
         <v>0.4012988812070913</v>
@@ -6147,7 +6147,7 @@
         <v>-1.315386399498972</v>
       </c>
       <c r="C336" t="n">
-        <v>-0.04706984423541187</v>
+        <v>-0.04243801116167915</v>
       </c>
       <c r="D336" t="n">
         <v>0.2692656463854147</v>
@@ -6164,7 +6164,7 @@
         <v>-1.232105420566099</v>
       </c>
       <c r="C337" t="n">
-        <v>-0.04248868081484558</v>
+        <v>-0.03692774043661936</v>
       </c>
       <c r="D337" t="n">
         <v>0.2201519689621168</v>
@@ -6181,7 +6181,7 @@
         <v>-1.078242244087746</v>
       </c>
       <c r="C338" t="n">
-        <v>-0.02351694915932823</v>
+        <v>-0.02134923865410661</v>
       </c>
       <c r="D338" t="n">
         <v>0.1470370271165108</v>
@@ -6198,7 +6198,7 @@
         <v>-0.9627195965964149</v>
       </c>
       <c r="C339" t="n">
-        <v>0.009301455898754887</v>
+        <v>0.0003254350348723328</v>
       </c>
       <c r="D339" t="n">
         <v>0.1763511896644202</v>
@@ -6215,7 +6215,7 @@
         <v>-0.9042649416713244</v>
       </c>
       <c r="C340" t="n">
-        <v>0.03660336726301534</v>
+        <v>0.01834838496226009</v>
       </c>
       <c r="D340" t="n">
         <v>0.1371594861448566</v>
@@ -6229,16 +6229,33 @@
         <v>45747</v>
       </c>
       <c r="B341" t="n">
-        <v>-0.8397481983321728</v>
+        <v>-0.8737728267695283</v>
       </c>
       <c r="C341" t="n">
-        <v>0.04503902734193773</v>
+        <v>0.0005865205272010107</v>
       </c>
       <c r="D341" t="n">
         <v>0.1110546272241258</v>
       </c>
       <c r="E341" t="n">
         <v>-0.1283410707788303</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B342" t="n">
+        <v>-0.8881880024222687</v>
+      </c>
+      <c r="C342" t="n">
+        <v>-0.02246363804680394</v>
+      </c>
+      <c r="D342" t="n">
+        <v>-0.1433469846859853</v>
+      </c>
+      <c r="E342" t="n">
+        <v>-0.2934007498358872</v>
       </c>
     </row>
   </sheetData>
